--- a/data/trans_orig/P36B13-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36B13-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79715</t>
+          <t>80201</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>112798</t>
+          <t>112757</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>87673</t>
+          <t>88341</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>120402</t>
+          <t>121581</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>176108</t>
+          <t>176538</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>224167</t>
+          <t>222342</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,28%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52710</t>
+          <t>51546</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82041</t>
+          <t>82852</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62529</t>
+          <t>63016</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>93163</t>
+          <t>92616</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>122961</t>
+          <t>122790</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>166751</t>
+          <t>164398</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,3%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>70455</t>
+          <t>69751</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>104847</t>
+          <t>104274</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53533</t>
+          <t>54396</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>81486</t>
+          <t>83514</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>132275</t>
+          <t>132218</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>177037</t>
+          <t>179272</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25868</t>
+          <t>25669</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48616</t>
+          <t>48577</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25939</t>
+          <t>25292</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47130</t>
+          <t>47890</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54666</t>
+          <t>56318</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89172</t>
+          <t>88206</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17143</t>
+          <t>16207</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12768</t>
+          <t>12787</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8294</t>
+          <t>7928</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24696</t>
+          <t>23158</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106530</t>
+          <t>105094</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>146308</t>
+          <t>144872</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>128615</t>
+          <t>127556</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>170001</t>
+          <t>170873</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>243134</t>
+          <t>246476</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>304558</t>
+          <t>305934</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,87%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>109630</t>
+          <t>110358</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>147945</t>
+          <t>150805</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132639</t>
+          <t>132782</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>177222</t>
+          <t>177394</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>255133</t>
+          <t>255434</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>311967</t>
+          <t>314058</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,66%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>159086</t>
+          <t>160534</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>203827</t>
+          <t>204435</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>157453</t>
+          <t>157007</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>201103</t>
+          <t>200782</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>331199</t>
+          <t>329992</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>396015</t>
+          <t>390254</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,1%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49192</t>
+          <t>48006</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78532</t>
+          <t>78224</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28030</t>
+          <t>27997</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52545</t>
+          <t>51045</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83716</t>
+          <t>84640</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121214</t>
+          <t>121978</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10466</t>
+          <t>11596</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12411</t>
+          <t>12503</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46507</t>
+          <t>45017</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71737</t>
+          <t>71491</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87475</t>
+          <t>85569</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119747</t>
+          <t>120461</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>138777</t>
+          <t>141038</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>182373</t>
+          <t>182103</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85100</t>
+          <t>84803</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>116686</t>
+          <t>117044</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99316</t>
+          <t>101602</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>134147</t>
+          <t>135885</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>195417</t>
+          <t>193715</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>243425</t>
+          <t>244125</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,45%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>81475</t>
+          <t>80834</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>112656</t>
+          <t>113024</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>67602</t>
+          <t>67395</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>97243</t>
+          <t>97378</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>156806</t>
+          <t>152736</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>200162</t>
+          <t>200102</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,69%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37811</t>
+          <t>37767</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>62546</t>
+          <t>61592</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21395</t>
+          <t>21697</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43617</t>
+          <t>42561</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65647</t>
+          <t>66325</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>99667</t>
+          <t>100106</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6609</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19217</t>
+          <t>18805</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>883</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7097</t>
+          <t>8022</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23198</t>
+          <t>22785</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>110441</t>
+          <t>109107</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>147551</t>
+          <t>147205</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>142232</t>
+          <t>144359</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>182903</t>
+          <t>186575</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>262414</t>
+          <t>261652</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>316103</t>
+          <t>317002</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,16%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>64123</t>
+          <t>63990</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>98105</t>
+          <t>95271</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>74646</t>
+          <t>73015</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>107521</t>
+          <t>107372</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>145266</t>
+          <t>145713</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>192659</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>97112</t>
+          <t>99739</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>134940</t>
+          <t>136424</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>90350</t>
+          <t>89116</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>124358</t>
+          <t>127783</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>198854</t>
+          <t>199385</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>250894</t>
+          <t>251203</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26731</t>
+          <t>26783</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50498</t>
+          <t>50760</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10649</t>
+          <t>11742</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28483</t>
+          <t>27548</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43637</t>
+          <t>43626</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>73034</t>
+          <t>72751</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3773</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16531</t>
+          <t>15998</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11232</t>
+          <t>11141</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20296</t>
+          <t>21594</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>52168</t>
+          <t>51913</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>79377</t>
+          <t>79563</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>66775</t>
+          <t>66348</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>94988</t>
+          <t>94379</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>127136</t>
+          <t>125107</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>164644</t>
+          <t>165118</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,59%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>64080</t>
+          <t>63585</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>90288</t>
+          <t>91338</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>68199</t>
+          <t>68477</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>96241</t>
+          <t>97265</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>139929</t>
+          <t>141907</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>179164</t>
+          <t>180308</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,14%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>38409</t>
+          <t>36596</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>62374</t>
+          <t>62549</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>32927</t>
+          <t>33630</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>54963</t>
+          <t>57078</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>76697</t>
+          <t>77135</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>109358</t>
+          <t>110422</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,81%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>11091</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>27780</t>
+          <t>28907</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>16717</t>
+          <t>18014</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>19063</t>
+          <t>19240</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>39934</t>
+          <t>39542</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>91059</t>
+          <t>91360</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>125361</t>
+          <t>123277</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>127935</t>
+          <t>129043</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>162025</t>
+          <t>161821</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>228834</t>
+          <t>228943</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>273604</t>
+          <t>275990</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,47%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>65259</t>
+          <t>68254</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>97110</t>
+          <t>98748</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>52761</t>
+          <t>51619</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>80385</t>
+          <t>80410</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>126389</t>
+          <t>126264</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>167528</t>
+          <t>167938</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>43905</t>
+          <t>44419</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>71644</t>
+          <t>72568</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>41425</t>
+          <t>40916</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>67215</t>
+          <t>66891</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>95389</t>
+          <t>92979</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>132253</t>
+          <t>129224</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>7546</t>
+          <t>7638</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>21036</t>
+          <t>21873</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>16752</t>
+          <t>16187</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>14886</t>
+          <t>14432</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>32413</t>
+          <t>32684</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>987</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>8014</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>982</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>8953</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>161441</t>
+          <t>160638</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>210440</t>
+          <t>209061</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>202682</t>
+          <t>202452</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>254531</t>
+          <t>253936</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>379697</t>
+          <t>377999</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>449606</t>
+          <t>450436</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>207108</t>
+          <t>209367</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>257654</t>
+          <t>262466</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>215696</t>
+          <t>214874</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>265156</t>
+          <t>267733</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>439914</t>
+          <t>436191</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>510681</t>
+          <t>507405</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,33%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>147123</t>
+          <t>148274</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>195105</t>
+          <t>195372</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>154011</t>
+          <t>154921</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>199033</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>318423</t>
+          <t>312813</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>383956</t>
+          <t>378862</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>35767</t>
+          <t>36482</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>64553</t>
+          <t>64619</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>23327</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>44781</t>
+          <t>45477</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>63219</t>
+          <t>65598</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>97872</t>
+          <t>101341</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>13291</t>
+          <t>13317</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>832</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>8821</t>
+          <t>8613</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4365</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>17299</t>
+          <t>17622</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>166810</t>
+          <t>166231</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>215439</t>
+          <t>214147</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>210328</t>
+          <t>209799</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>263655</t>
+          <t>264478</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>384478</t>
+          <t>389763</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>461052</t>
+          <t>463036</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>200597</t>
+          <t>203793</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>252426</t>
+          <t>252451</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>231921</t>
+          <t>228716</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>284980</t>
+          <t>285060</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>449261</t>
+          <t>447285</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>522609</t>
+          <t>522853</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,72%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>225055</t>
+          <t>227916</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>279417</t>
+          <t>282303</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>214411</t>
+          <t>214328</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>266009</t>
+          <t>267216</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>456881</t>
+          <t>454312</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>531767</t>
+          <t>528533</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,07%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>89743</t>
+          <t>89198</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>127949</t>
+          <t>128229</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>60166</t>
+          <t>61235</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>96927</t>
+          <t>95830</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>158555</t>
+          <t>159584</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>210897</t>
+          <t>210346</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>6413</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>15953</t>
+          <t>16664</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>18446</t>
+          <t>19696</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>897334</t>
+          <t>899003</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>1001461</t>
+          <t>1004642</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1153062</t>
+          <t>1151031</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1276601</t>
+          <t>1270230</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>2077914</t>
+          <t>2083449</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>2243588</t>
+          <t>2238168</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,46%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>936667</t>
+          <t>935850</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>1045827</t>
+          <t>1046921</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>1023676</t>
+          <t>1029472</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>1138553</t>
+          <t>1138552</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>2002530</t>
+          <t>1998594</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>2156320</t>
+          <t>2154891</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>961804</t>
+          <t>961148</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>1067920</t>
+          <t>1071612</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>897494</t>
+          <t>899730</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1003386</t>
+          <t>1009133</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>1888142</t>
+          <t>1885584</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>2032748</t>
+          <t>2039403</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>338724</t>
+          <t>338570</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>412252</t>
+          <t>411121</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>222887</t>
+          <t>219845</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>280751</t>
+          <t>279759</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>580748</t>
+          <t>576099</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>672448</t>
+          <t>670743</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>34685</t>
+          <t>33937</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>61061</t>
+          <t>60979</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>17366</t>
+          <t>17628</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>37412</t>
+          <t>36039</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>55902</t>
+          <t>56560</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>89227</t>
+          <t>89736</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -7100,32 +7100,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>116182</t>
+          <t>127196</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95592</t>
+          <t>108980</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>132880</t>
+          <t>144125</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7135,32 +7135,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>140866</t>
+          <t>149204</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>126323</t>
+          <t>134578</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>155102</t>
+          <t>162707</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7170,32 +7170,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>257048</t>
+          <t>276400</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>233628</t>
+          <t>254905</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>284478</t>
+          <t>300650</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,35%</t>
         </is>
       </c>
     </row>
@@ -7213,32 +7213,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>168193</t>
+          <t>159606</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>148872</t>
+          <t>139522</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>191470</t>
+          <t>178251</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7248,32 +7248,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>124800</t>
+          <t>140476</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>111150</t>
+          <t>125965</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139683</t>
+          <t>154310</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7283,32 +7283,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>292993</t>
+          <t>300082</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>265831</t>
+          <t>276378</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>319638</t>
+          <t>324151</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>51,06%</t>
         </is>
       </c>
     </row>
@@ -7326,32 +7326,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27068</t>
+          <t>32043</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16939</t>
+          <t>21903</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42819</t>
+          <t>45008</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7361,32 +7361,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22403</t>
+          <t>25293</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>16222</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37547</t>
+          <t>38867</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7396,32 +7396,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>49471</t>
+          <t>57336</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35685</t>
+          <t>43205</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>72771</t>
+          <t>76377</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -7484,12 +7484,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8879</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -7519,12 +7519,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8874</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -7665,17 +7665,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7700,17 +7700,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7735,17 +7735,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7782,32 +7782,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>127312</t>
+          <t>132111</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>108086</t>
+          <t>109754</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154303</t>
+          <t>155302</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7817,32 +7817,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>187343</t>
+          <t>197678</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>168360</t>
+          <t>180046</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>205786</t>
+          <t>217229</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7852,32 +7852,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>314656</t>
+          <t>329790</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>284721</t>
+          <t>300236</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>343908</t>
+          <t>360648</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -7895,32 +7895,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>230992</t>
+          <t>243887</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>201790</t>
+          <t>215709</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>260303</t>
+          <t>271350</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7930,32 +7930,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>209494</t>
+          <t>219170</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>188748</t>
+          <t>196335</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>229057</t>
+          <t>239498</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7965,32 +7965,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>440485</t>
+          <t>463058</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>402393</t>
+          <t>425721</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>473797</t>
+          <t>497669</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>46,26%</t>
         </is>
       </c>
     </row>
@@ -8008,32 +8008,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>139963</t>
+          <t>134184</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>113003</t>
+          <t>108485</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>171118</t>
+          <t>165188</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8043,32 +8043,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>104349</t>
+          <t>115589</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>88216</t>
+          <t>95417</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>123342</t>
+          <t>135680</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8078,32 +8078,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>244312</t>
+          <t>249773</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>212170</t>
+          <t>219206</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>279252</t>
+          <t>283632</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,37%</t>
         </is>
       </c>
     </row>
@@ -8121,17 +8121,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18628</t>
+          <t>19041</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9490</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36511</t>
+          <t>36003</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8156,22 +8156,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11672</t>
+          <t>11968</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19373</t>
+          <t>20553</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -8191,32 +8191,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>30300</t>
+          <t>31008</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18161</t>
+          <t>18867</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48530</t>
+          <t>46851</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6524</t>
+          <t>7134</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>703</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2219</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8934</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -8347,17 +8347,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8382,17 +8382,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>513581</t>
+          <t>545109</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>513581</t>
+          <t>545109</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>513581</t>
+          <t>545109</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8417,17 +8417,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1031971</t>
+          <t>1075756</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1031971</t>
+          <t>1075756</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1031971</t>
+          <t>1075756</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8464,32 +8464,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>80777</t>
+          <t>82071</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66762</t>
+          <t>69732</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>94472</t>
+          <t>98024</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8499,32 +8499,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>120033</t>
+          <t>121436</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>105194</t>
+          <t>108304</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>136007</t>
+          <t>136100</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8534,32 +8534,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>200811</t>
+          <t>203507</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>180787</t>
+          <t>184436</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>223885</t>
+          <t>225312</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,02%</t>
         </is>
       </c>
     </row>
@@ -8577,32 +8577,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>116887</t>
+          <t>116459</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>100195</t>
+          <t>101497</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134075</t>
+          <t>134544</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8612,32 +8612,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>126087</t>
+          <t>129741</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>111338</t>
+          <t>114708</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>143147</t>
+          <t>146328</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8647,32 +8647,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>242974</t>
+          <t>246201</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>222171</t>
+          <t>222967</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>267454</t>
+          <t>270283</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,8%</t>
         </is>
       </c>
     </row>
@@ -8690,32 +8690,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>100837</t>
+          <t>100568</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>84846</t>
+          <t>83514</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>119307</t>
+          <t>115839</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8725,32 +8725,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>83100</t>
+          <t>85312</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>70041</t>
+          <t>72204</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>96793</t>
+          <t>100735</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8760,32 +8760,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>183937</t>
+          <t>185880</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>161673</t>
+          <t>165283</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>206479</t>
+          <t>208140</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -8803,32 +8803,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12511</t>
+          <t>11946</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22281</t>
+          <t>20364</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8838,32 +8838,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12821</t>
+          <t>12920</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20400</t>
+          <t>21102</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8873,32 +8873,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>25331</t>
+          <t>24866</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16594</t>
+          <t>16331</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36584</t>
+          <t>35794</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>866</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8926,84 +8926,84 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3863</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1932</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>6573</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1097</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>3666</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>5983</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,07%</t>
@@ -9011,7 +9011,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -9029,17 +9029,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>311904</t>
+          <t>311911</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>311904</t>
+          <t>311911</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>311904</t>
+          <t>311911</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9064,17 +9064,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>343138</t>
+          <t>350475</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>343138</t>
+          <t>350475</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>343138</t>
+          <t>350475</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9099,17 +9099,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>655042</t>
+          <t>662386</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>655042</t>
+          <t>662386</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>655042</t>
+          <t>662386</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9146,32 +9146,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>70814</t>
+          <t>81500</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55635</t>
+          <t>65838</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86183</t>
+          <t>100403</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9181,32 +9181,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>126517</t>
+          <t>144488</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>72986</t>
+          <t>126281</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>160908</t>
+          <t>162359</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9216,32 +9216,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>197332</t>
+          <t>225988</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>141553</t>
+          <t>202166</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>232313</t>
+          <t>253154</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>31,84%</t>
         </is>
       </c>
     </row>
@@ -9259,32 +9259,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>135366</t>
+          <t>157021</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>113559</t>
+          <t>131751</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>181108</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9294,32 +9294,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>155666</t>
+          <t>173651</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>98181</t>
+          <t>154243</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>199623</t>
+          <t>193763</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9329,32 +9329,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>291031</t>
+          <t>330673</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>208765</t>
+          <t>298150</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>336266</t>
+          <t>362634</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -9372,32 +9372,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>90556</t>
+          <t>111778</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>71137</t>
+          <t>90673</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>118698</t>
+          <t>140347</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9407,32 +9407,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>187682</t>
+          <t>96846</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>112693</t>
+          <t>80026</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>301495</t>
+          <t>117548</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9442,32 +9442,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>278238</t>
+          <t>208624</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>205208</t>
+          <t>179179</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>418687</t>
+          <t>243294</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>30,6%</t>
         </is>
       </c>
     </row>
@@ -9485,32 +9485,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>15821</t>
+          <t>22845</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7490</t>
+          <t>12083</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30471</t>
+          <t>41550</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9520,32 +9520,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>4988</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1577</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9254</t>
+          <t>10169</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9555,32 +9555,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>19860</t>
+          <t>27833</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11002</t>
+          <t>16014</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37873</t>
+          <t>46105</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>6929</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -9678,12 +9678,12 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6062</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -9711,17 +9711,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9746,17 +9746,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9781,17 +9781,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9828,32 +9828,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>27032</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>15572</t>
+          <t>18739</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>30472</t>
+          <t>37799</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9863,32 +9863,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>22093</t>
+          <t>23073</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>17368</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>29003</t>
+          <t>29518</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9898,32 +9898,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>44534</t>
+          <t>50105</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>36185</t>
+          <t>40868</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>54602</t>
+          <t>61080</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -9941,32 +9941,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>108866</t>
+          <t>122763</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>97426</t>
+          <t>108857</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>119905</t>
+          <t>134257</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9976,32 +9976,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>139798</t>
+          <t>152661</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>130739</t>
+          <t>141898</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>149139</t>
+          <t>162482</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10011,32 +10011,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>248664</t>
+          <t>275424</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>233475</t>
+          <t>260352</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>262098</t>
+          <t>293521</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,94%</t>
         </is>
       </c>
     </row>
@@ -10054,32 +10054,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>44465</t>
+          <t>52612</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>35210</t>
+          <t>42643</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>56864</t>
+          <t>63524</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10089,32 +10089,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>44127</t>
+          <t>48764</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>35857</t>
+          <t>40203</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>52241</t>
+          <t>59764</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10124,32 +10124,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>88592</t>
+          <t>101376</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>76343</t>
+          <t>87229</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>103454</t>
+          <t>116854</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -10167,32 +10167,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10202,32 +10202,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>705</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10237,32 +10237,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2314</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>9728</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -10393,17 +10393,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -10428,17 +10428,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>207860</t>
+          <t>226391</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>207860</t>
+          <t>226391</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>207860</t>
+          <t>226391</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -10463,17 +10463,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>386601</t>
+          <t>432056</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>386601</t>
+          <t>432056</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>386601</t>
+          <t>432056</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -10510,32 +10510,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>83545</t>
+          <t>84363</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>71604</t>
+          <t>72570</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>96091</t>
+          <t>98299</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10545,32 +10545,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>104352</t>
+          <t>107813</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>93717</t>
+          <t>94753</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>117033</t>
+          <t>119801</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10580,32 +10580,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>187897</t>
+          <t>192176</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>172565</t>
+          <t>174349</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>208061</t>
+          <t>208577</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,03%</t>
         </is>
       </c>
     </row>
@@ -10623,32 +10623,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>103087</t>
+          <t>106576</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>88947</t>
+          <t>92316</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>117798</t>
+          <t>120456</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10658,32 +10658,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>113351</t>
+          <t>115905</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>101088</t>
+          <t>102864</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>127797</t>
+          <t>129074</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10693,32 +10693,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>216438</t>
+          <t>222482</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>197434</t>
+          <t>203768</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>237172</t>
+          <t>242620</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>45,4%</t>
         </is>
       </c>
     </row>
@@ -10736,32 +10736,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>73715</t>
+          <t>71201</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>59971</t>
+          <t>57432</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>89187</t>
+          <t>85498</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10771,32 +10771,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>37947</t>
+          <t>38613</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>28203</t>
+          <t>29631</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>48873</t>
+          <t>50742</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10806,32 +10806,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>111662</t>
+          <t>109814</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>94717</t>
+          <t>92970</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>130146</t>
+          <t>127603</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -10849,32 +10849,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>8447</t>
+          <t>7765</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3628</t>
+          <t>3330</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>18079</t>
+          <t>16226</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10884,7 +10884,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10919,22 +10919,22 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>9183</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4397</t>
+          <t>4413</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>18911</t>
+          <t>18227</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -10944,7 +10944,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -10962,7 +10962,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>802</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -10972,12 +10972,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -10987,7 +10987,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>802</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -11075,17 +11075,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -11110,17 +11110,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -11145,17 +11145,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -11192,32 +11192,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>190056</t>
+          <t>219430</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>166990</t>
+          <t>193238</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>218075</t>
+          <t>246601</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11227,32 +11227,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>453324</t>
+          <t>301651</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>319124</t>
+          <t>278696</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>650373</t>
+          <t>328199</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11262,32 +11262,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>643380</t>
+          <t>521082</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>499378</t>
+          <t>485703</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>953913</t>
+          <t>557163</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>37,39%</t>
         </is>
       </c>
     </row>
@@ -11305,32 +11305,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>216014</t>
+          <t>246989</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>189466</t>
+          <t>218719</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>245287</t>
+          <t>276449</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11340,32 +11340,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>222365</t>
+          <t>269455</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>109783</t>
+          <t>244956</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>303221</t>
+          <t>293965</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11375,32 +11375,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>438379</t>
+          <t>516444</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>271095</t>
+          <t>476259</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>522553</t>
+          <t>553514</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>37,14%</t>
         </is>
       </c>
     </row>
@@ -11418,32 +11418,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>153386</t>
+          <t>182488</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>128366</t>
+          <t>155149</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>181110</t>
+          <t>212983</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>141278</t>
+          <t>161151</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>68026</t>
+          <t>136339</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>194248</t>
+          <t>184731</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11488,32 +11488,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>294664</t>
+          <t>343639</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>175156</t>
+          <t>306666</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>355058</t>
+          <t>383091</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>25,71%</t>
         </is>
       </c>
     </row>
@@ -11531,32 +11531,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>47904</t>
+          <t>52466</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>30661</t>
+          <t>36138</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>70061</t>
+          <t>75351</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>29103</t>
+          <t>33241</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>12198</t>
+          <t>23265</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>46872</t>
+          <t>48968</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11601,32 +11601,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>77007</t>
+          <t>85707</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>46323</t>
+          <t>67044</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>104464</t>
+          <t>112407</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -11644,32 +11644,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>16918</t>
+          <t>18314</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>9320</t>
+          <t>10503</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>27407</t>
+          <t>30347</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11679,32 +11679,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5383</t>
+          <t>13572</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11714,32 +11714,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>18664</t>
+          <t>23297</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>9719</t>
+          <t>13962</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>31322</t>
+          <t>36337</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -11757,17 +11757,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -11792,17 +11792,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>847815</t>
+          <t>770481</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>847815</t>
+          <t>770481</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>847815</t>
+          <t>770481</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -11827,17 +11827,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1472095</t>
+          <t>1490168</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1472095</t>
+          <t>1490168</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1472095</t>
+          <t>1490168</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>143675</t>
+          <t>166346</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>63198</t>
+          <t>143062</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>203014</t>
+          <t>188718</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>200816</t>
+          <t>237825</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>180770</t>
+          <t>213875</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>221667</t>
+          <t>259062</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11944,32 +11944,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>344491</t>
+          <t>404171</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>214338</t>
+          <t>373282</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>417016</t>
+          <t>435921</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -11987,32 +11987,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>194565</t>
+          <t>226391</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>85854</t>
+          <t>200377</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>275584</t>
+          <t>255219</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12022,32 +12022,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>226871</t>
+          <t>259118</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>206638</t>
+          <t>235630</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>247332</t>
+          <t>282525</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12057,32 +12057,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>421436</t>
+          <t>485510</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>265545</t>
+          <t>452828</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>508364</t>
+          <t>524762</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -12100,32 +12100,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>239648</t>
+          <t>280286</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>108120</t>
+          <t>248102</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>334580</t>
+          <t>308042</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12135,32 +12135,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>231553</t>
+          <t>266267</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>209930</t>
+          <t>241549</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>255116</t>
+          <t>292623</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12170,32 +12170,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>471201</t>
+          <t>546553</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>276176</t>
+          <t>509894</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>566430</t>
+          <t>584080</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>35,85%</t>
         </is>
       </c>
     </row>
@@ -12213,32 +12213,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>93588</t>
+          <t>110061</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>39760</t>
+          <t>88416</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>137296</t>
+          <t>135425</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12248,32 +12248,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>54796</t>
+          <t>63746</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>41263</t>
+          <t>50264</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>68735</t>
+          <t>81072</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12283,32 +12283,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>148384</t>
+          <t>173807</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>95813</t>
+          <t>148482</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>188047</t>
+          <t>201891</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -12326,32 +12326,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>257245</t>
+          <t>14988</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>12902</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>624725</t>
+          <t>27030</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12361,32 +12361,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>3695</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>10253</t>
+          <t>12341</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12396,32 +12396,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>260940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>15938</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>780423</t>
+          <t>29794</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -12439,17 +12439,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12474,17 +12474,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -12509,17 +12509,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -12556,32 +12556,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>834803</t>
+          <t>920049</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>614773</t>
+          <t>863882</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>917807</t>
+          <t>980071</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12591,32 +12591,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>1355346</t>
+          <t>1283169</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1189617</t>
+          <t>1236670</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1757464</t>
+          <t>1332745</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12626,32 +12626,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>2190148</t>
+          <t>2203219</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>1961109</t>
+          <t>2124183</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>2712969</t>
+          <t>2269486</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>31,28%</t>
         </is>
       </c>
     </row>
@@ -12669,32 +12669,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>1273970</t>
+          <t>1379694</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>933861</t>
+          <t>1318938</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>1389789</t>
+          <t>1448922</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12704,32 +12704,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>1318430</t>
+          <t>1460178</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>1073259</t>
+          <t>1406293</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>1431180</t>
+          <t>1512560</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12739,32 +12739,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>2592400</t>
+          <t>2839873</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>2244608</t>
+          <t>2754922</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>2778971</t>
+          <t>2918886</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>40,24%</t>
         </is>
       </c>
     </row>
@@ -12782,32 +12782,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>869637</t>
+          <t>965159</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>686162</t>
+          <t>899851</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>956248</t>
+          <t>1028300</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12817,32 +12817,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>852439</t>
+          <t>837836</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>719237</t>
+          <t>794643</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1025998</t>
+          <t>890390</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12852,32 +12852,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>1722076</t>
+          <t>1802995</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>1511104</t>
+          <t>1729827</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>1922434</t>
+          <t>1880143</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -12895,32 +12895,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>199870</t>
+          <t>227382</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>154996</t>
+          <t>193132</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>237981</t>
+          <t>267863</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12930,32 +12930,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>117243</t>
+          <t>131262</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>92219</t>
+          <t>109331</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>141364</t>
+          <t>156911</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12965,32 +12965,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>317113</t>
+          <t>358644</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>266273</t>
+          <t>314570</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>367453</t>
+          <t>405004</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -13008,32 +13008,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>277391</t>
+          <t>36395</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>31995</t>
+          <t>25454</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1070221</t>
+          <t>53642</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13043,32 +13043,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>7655</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>16828</t>
+          <t>24682</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13078,32 +13078,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>286466</t>
+          <t>49509</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>36958</t>
+          <t>35386</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1124660</t>
+          <t>68136</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -13121,17 +13121,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>3455671</t>
+          <t>3528680</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>3455671</t>
+          <t>3528680</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>3455671</t>
+          <t>3528680</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13156,17 +13156,17 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>3652534</t>
+          <t>3725560</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>3652534</t>
+          <t>3725560</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3652534</t>
+          <t>3725560</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -13191,17 +13191,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>7108204</t>
+          <t>7254240</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>7108204</t>
+          <t>7254240</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>7108204</t>
+          <t>7254240</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
